--- a/src/model/prompt_tests/prompt1_test.xlsx
+++ b/src/model/prompt_tests/prompt1_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bruce/Desktop/APCOMP 215/AC215_888/src/model/prompt_tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9EE94C-C3ED-154B-808D-161E683D48D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5534A1-522F-D04E-8BB0-E5DD84E20B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="680" windowWidth="28100" windowHeight="16880" xr2:uid="{60DE08AB-C148-5C4E-A3EA-40F02C48914F}"/>
   </bookViews>
@@ -38,11 +38,11 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>A patient with tuberculosis receiving isoniazid therapy under directly observed treatment developed acute hepatitis after 3 months. Liver enzymes were monitored monthly and were normal until the week prior. The medication was discontinued immediately, but the patient developed hepatic failure requiring transfer for transplant evaluation.</t>
+    <t>A patient was admitted to the critical care unit with congestive heart failure and later has a new complaint of chest pain persisting over several hours. Tylenol is administered but does not decrease the patient’s pain scale rating. The Resident orders a laboratory work-up. An EKG shows that the patient is experiencing an acute ST-elevation myocardial infarction. The attending cardiologist is called, but does not respond to multiple pages. The nurse does not escalate the patient’s emergent condition to other physicians or the rapid response team. The patient continues to decompensate, codes and expires.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A patient was admitted to the critical care unit with congestive heart failure and later has a new complaint of chest pain persisting over several hours. Tylenol is administered but does not decrease the patient’s pain scale rating. The Resident orders a laboratory work-up. An EKG shows that the patient is experiencing an acute ST-elevation myocardial infarction. The attending cardiologist is called, but does not respond to multiple pages. The nurse does not escalate the patient’s emergent condition to other physicians or the rapid response team. The patient continues to decompensate, codes and expires.</t>
+    <t>A 65-year-old man underwent laparoscopic cholecystectomy. His chronic warfarin therapy was appropriately managed preoperatively and restarted on postoperative day 2. On day 4, he developed mild wound bleeding and was found to have supratherapeutic INR. Vitamin K was given, and bleeding resolved without further intervention.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,13 +438,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="170">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" ht="289">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1"/>
     </row>
